--- a/港岛-山顶区-宾吉道3号/宾吉道3号_销控明细表.xlsx
+++ b/港岛-山顶区-宾吉道3号/宾吉道3号_销控明细表.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -98,11 +98,6 @@
       <b val="1"/>
       <color rgb="00000000"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="8"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -186,7 +181,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -233,13 +228,10 @@
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -607,7 +599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -684,7 +676,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>A号屋</t>
+          <t>B号屋</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -703,11 +695,11 @@
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>4893</v>
+        <v>4565</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -715,15 +707,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H3" s="5" t="n">
+        <v>471900000</v>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>103373</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -734,7 +722,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>B号屋</t>
+          <t>C号屋</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -753,7 +741,7 @@
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>4565</v>
+        <v>4600</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -766,10 +754,10 @@
         </is>
       </c>
       <c r="H4" s="5" t="n">
-        <v>471900000</v>
+        <v>454960000</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>103373</v>
+        <v>98904</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
@@ -780,7 +768,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>C号屋</t>
+          <t>D号屋</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -795,11 +783,11 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>4600</v>
+        <v>4561</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -812,10 +800,10 @@
         </is>
       </c>
       <c r="H5" s="5" t="n">
-        <v>454960000</v>
+        <v>451330000</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>98904</v>
+        <v>98954</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -826,7 +814,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>D号屋</t>
+          <t>E号屋</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -841,11 +829,11 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>4561</v>
+        <v>4432</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -858,10 +846,10 @@
         </is>
       </c>
       <c r="H6" s="5" t="n">
-        <v>451330000</v>
+        <v>459800000</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>98954</v>
+        <v>103745</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
@@ -872,7 +860,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>E号屋</t>
+          <t>F号屋</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -891,11 +879,11 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>4432</v>
+        <v>4850</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -904,58 +892,12 @@
         </is>
       </c>
       <c r="H7" s="5" t="n">
-        <v>459800000</v>
+        <v>503360000</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>103745</v>
+        <v>103786</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>F号屋</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>4850</v>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="n">
-        <v>503360000</v>
-      </c>
-      <c r="I8" s="5" t="n">
-        <v>103786</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -976,7 +918,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -985,7 +927,6 @@
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -1030,7 +971,7 @@
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>6 套</t>
+          <t>5 套</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
@@ -1055,7 +996,7 @@
       </c>
       <c r="F3" s="11" t="inlineStr">
         <is>
-          <t>1 套</t>
+          <t>0 套</t>
         </is>
       </c>
     </row>
@@ -1067,30 +1008,25 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>A号屋</t>
+          <t>B号屋</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>B号屋</t>
+          <t>C号屋</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>C号屋</t>
+          <t>D号屋</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>D号屋</t>
+          <t>E号屋</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E号屋</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>F号屋</t>
         </is>
@@ -1103,15 +1039,6 @@
         </is>
       </c>
       <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A号屋
-4893呎 (4+房)
-(待售)
-暂无价格
-暂无呎价</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>B号屋
 4565呎 (4+房)
@@ -1120,7 +1047,7 @@
 $103,373/呎</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t>C号屋
 4600呎 (4+房)
@@ -1129,7 +1056,7 @@
 $98,904/呎</t>
         </is>
       </c>
-      <c r="E6" s="17" t="inlineStr">
+      <c r="D6" s="16" t="inlineStr">
         <is>
           <t>D号屋
 4561呎 (3房)
@@ -1138,7 +1065,7 @@
 $98,954/呎</t>
         </is>
       </c>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="E6" s="16" t="inlineStr">
         <is>
           <t>E号屋
 4432呎 (4+房)
@@ -1147,7 +1074,7 @@
 $103,745/呎</t>
         </is>
       </c>
-      <c r="G6" s="18" t="inlineStr">
+      <c r="F6" s="17" t="inlineStr">
         <is>
           <t>F号屋
 4850呎 (4+房)
@@ -1159,7 +1086,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>

--- a/港岛-山顶区-宾吉道3号/宾吉道3号_销控明细表.xlsx
+++ b/港岛-山顶区-宾吉道3号/宾吉道3号_销控明细表.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -98,6 +98,11 @@
       <b val="1"/>
       <color rgb="00000000"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -181,7 +186,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -228,10 +233,13 @@
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -599,7 +607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -676,7 +684,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>B号屋</t>
+          <t>A号屋</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -695,11 +703,11 @@
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>4565</v>
+        <v>4893</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -707,11 +715,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H3" s="5" t="n">
-        <v>471900000</v>
-      </c>
-      <c r="I3" s="5" t="n">
-        <v>103373</v>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -722,7 +734,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>C号屋</t>
+          <t>B号屋</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -741,7 +753,7 @@
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>4600</v>
+        <v>4565</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -754,10 +766,10 @@
         </is>
       </c>
       <c r="H4" s="5" t="n">
-        <v>454960000</v>
+        <v>471900000</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>98904</v>
+        <v>103373</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
@@ -768,7 +780,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>D号屋</t>
+          <t>C号屋</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -783,11 +795,11 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>4561</v>
+        <v>4600</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -800,10 +812,10 @@
         </is>
       </c>
       <c r="H5" s="5" t="n">
-        <v>451330000</v>
+        <v>454960000</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>98954</v>
+        <v>98904</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -814,7 +826,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>E号屋</t>
+          <t>D号屋</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -829,11 +841,11 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>4432</v>
+        <v>4561</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -846,10 +858,10 @@
         </is>
       </c>
       <c r="H6" s="5" t="n">
-        <v>459800000</v>
+        <v>451330000</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>103745</v>
+        <v>98954</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
@@ -860,44 +872,90 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
+          <t>E号屋</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>4432</v>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>459800000</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>103745</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
           <t>F号屋</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>4+房</t>
         </is>
       </c>
-      <c r="E7" s="4" t="n">
+      <c r="E8" s="4" t="n">
         <v>4850</v>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>已定价未售</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="n">
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="n">
         <v>503360000</v>
       </c>
-      <c r="I7" s="5" t="n">
+      <c r="I8" s="5" t="n">
         <v>103786</v>
       </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -918,7 +976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -927,6 +985,7 @@
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -971,7 +1030,7 @@
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>5 套</t>
+          <t>6 套</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
@@ -996,7 +1055,7 @@
       </c>
       <c r="F3" s="11" t="inlineStr">
         <is>
-          <t>0 套</t>
+          <t>1 套</t>
         </is>
       </c>
     </row>
@@ -1008,25 +1067,30 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
+          <t>A号屋</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
           <t>B号屋</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>C号屋</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>D号屋</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>E号屋</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>F号屋</t>
         </is>
@@ -1039,6 +1103,15 @@
         </is>
       </c>
       <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>A号屋
+4893呎 (4+房)
+(待售)
+暂无价格
+暂无呎价</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>B号屋
 4565呎 (4+房)
@@ -1047,7 +1120,7 @@
 $103,373/呎</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>C号屋
 4600呎 (4+房)
@@ -1056,7 +1129,7 @@
 $98,904/呎</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="E6" s="17" t="inlineStr">
         <is>
           <t>D号屋
 4561呎 (3房)
@@ -1065,7 +1138,7 @@
 $98,954/呎</t>
         </is>
       </c>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="F6" s="17" t="inlineStr">
         <is>
           <t>E号屋
 4432呎 (4+房)
@@ -1074,7 +1147,7 @@
 $103,745/呎</t>
         </is>
       </c>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="G6" s="18" t="inlineStr">
         <is>
           <t>F号屋
 4850呎 (4+房)
@@ -1086,7 +1159,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
